--- a/resources/city/city.xlsx
+++ b/resources/city/city.xlsx
@@ -7736,35 +7736,45 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="35" t="inlineStr">
-        <is>
-          <t>key:1</t>
-        </is>
-      </c>
-      <c r="B64" s="35" t="inlineStr">
-        <is>
-          <t>key:1</t>
-        </is>
-      </c>
+      <c r="A64" s="35" t="n">
+        <v>510</v>
+      </c>
+      <c r="B64" s="35" t="n"/>
       <c r="C64" s="35" t="n"/>
-      <c r="D64" s="35" t="n"/>
+      <c r="D64" s="35" t="n">
+        <v>22300</v>
+      </c>
       <c r="E64" s="35" t="n"/>
       <c r="F64" s="35" t="n"/>
       <c r="G64" s="35" t="n"/>
     </row>
     <row r="65">
-      <c r="A65" s="35" t="n"/>
-      <c r="B65" s="35" t="n"/>
+      <c r="A65" s="35" t="inlineStr">
+        <is>
+          <t>key:1</t>
+        </is>
+      </c>
+      <c r="B65" s="35" t="inlineStr">
+        <is>
+          <t>key:1</t>
+        </is>
+      </c>
       <c r="C65" s="35" t="n"/>
       <c r="D65" s="35" t="n"/>
       <c r="E65" s="35" t="n"/>
       <c r="F65" s="35" t="n"/>
-      <c r="G65" s="35" t="n">
+      <c r="G65" s="35" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="35" t="n"/>
+      <c r="B66" s="35" t="n"/>
+      <c r="C66" s="35" t="n"/>
+      <c r="D66" s="35" t="n"/>
+      <c r="E66" s="35" t="n"/>
+      <c r="F66" s="35" t="n"/>
+      <c r="G66" s="35" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="0" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="0" t="n"/>
